--- a/data/seed/portfolio/L-2024-5384/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-5384/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I195"/>
+  <dimension ref="A1:I149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -560,38 +560,38 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>1133000</v>
+        <v>1335000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Barakali Non MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>350334106</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000148666189001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9138 02.07.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №6077 от 01.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -599,40 +599,40 @@
           <t>101</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
-        <v>1649000</v>
-      </c>
+      <c r="C11" s="2" t="n">
+        <v>18462000</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omad Farm Savdo MChJ</t>
+          <t>Saodat Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>268876078</t>
+          <t>327320639</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000357443680001</t>
+          <t>20208000060946953001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2909 03.07.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №9921</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -640,40 +640,40 @@
           <t>102</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n">
-        <v>1312000</v>
-      </c>
+      <c r="C12" s="2" t="n">
+        <v>39222000</v>
+      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Ishonch Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>331078117</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000408581523001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №135/26, QQS 12%</t>
+          <t>Предоплата за материалы по дог. №108/26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -683,38 +683,38 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>891000</v>
+        <v>10574000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Nihol Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>293888739</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000515912499001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №95/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №5424 от 02.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -724,21 +724,21 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>3085000</v>
+        <v>2344000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -748,14 +748,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8299</t>
+          <t>Оплата по с/ф №9756 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -763,33 +763,33 @@
           <t>105</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>3709000</v>
-      </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n">
+        <v>3603000</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>383089429</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000641564675001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №220/26</t>
+          <t>Оплата за продукцию по договору №154/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -804,28 +804,33 @@
           <t>106</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>14977000</v>
-      </c>
-      <c r="D16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n">
+        <v>8577000</v>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Saodat Metall Servis AJ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Оплата по с/ф №8519 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -840,40 +845,40 @@
           <t>107</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>27064000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>3713000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sarbon Trans Servis XK</t>
+          <t>Shodlik Mato MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>274109191</t>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000617602800001</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №51/26, QQS bilan</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №2811 ОТ 06.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -881,40 +886,35 @@
           <t>108</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n">
-        <v>1545000</v>
-      </c>
+      <c r="C18" s="2" t="n">
+        <v>14977000</v>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chust Qog'oz AJ</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>259242091</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000318952522001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №1107 07.07.2026, QQS bilan</t>
+          <t>Iyun oyi uchun ish haqi, reestr №8056</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1146000</v>
+        <v>36535000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saodat Qurilish Materiallari XK</t>
+          <t>Ishonch Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>316213871</t>
+          <t>331078117</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000814220025001</t>
+          <t>20208000408581523001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -948,14 +948,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №78/26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -965,21 +965,21 @@
       </c>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n">
-        <v>1764000</v>
+        <v>6252000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -989,14 +989,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №53/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №6705 от 07.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1004,40 +1004,40 @@
           <t>111</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n">
-        <v>1061000</v>
-      </c>
+      <c r="C21" s="2" t="n">
+        <v>1146000</v>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Durdona Mehmonxona MChJ</t>
+          <t>Zarafshon Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>360938887</t>
+          <t>267719662</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000915159124001</t>
+          <t>20208000691515883001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5923 08.07.2026, QQS bilan</t>
+          <t>IJARA HAQI IYUL OYI UCHUN, SHARTNOMA №20/23</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1045,40 +1045,40 @@
           <t>112</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>3926000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>2179000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Xiva Agro MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>290633879</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000332213541001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Shartnoma №81/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за транспортные услуги по договору №175/26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1088,21 +1088,21 @@
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>2695000</v>
+        <v>4208000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Omad Farm Savdo MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>268876078</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000357443680001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1112,14 +1112,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №89/26, QQS 12%</t>
+          <t>Оплата по с/ф №5232 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1129,38 +1129,38 @@
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>1800000</v>
+        <v>1147000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Shodlik Mato MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №114/26 от 09.07.2026</t>
+          <t>Предоплата за товар по договору №166/26 от 08.07.2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1168,35 +1168,40 @@
           <t>115</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>5800000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>11544000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-5384)</t>
+          <t>Saodat Metall Servis AJ</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>16307000252614105417</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-5384 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Shartnoma №75/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1204,40 +1209,40 @@
           <t>116</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>26936000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>1882000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Olmaliq Qurilish Materiallari XK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>327400977</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000272549219001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Shartnoma №201/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товары согласно счет-фактуре №6591</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1245,33 +1250,28 @@
           <t>117</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>21207000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>293754344</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-5384)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>16307000252614105417</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплатаза продукцию по дог. №117/26, НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-5384 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
@@ -1288,21 +1288,21 @@
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>2204000</v>
+        <v>16148000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №146/26, QQS 12%</t>
+          <t>Оплата по с/ф №1749 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -1327,33 +1327,33 @@
           <t>119</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>6234000</v>
-      </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n">
+        <v>2229000</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sarbon Trans Servis XK</t>
+          <t>Nihol Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>274109191</t>
+          <t>293888739</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000617602800001</t>
+          <t>20208000515912499001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №48/26, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartn. №155/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -1368,33 +1368,33 @@
           <t>120</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>6865000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>1993000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Nihol Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>383089429</t>
+          <t>293888739</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000641564675001</t>
+          <t>20208000515912499001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №1/26</t>
+          <t>Оплата по счет-фактуре №8819 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -1409,40 +1409,40 @@
           <t>121</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>9340000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>1339000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oydin Avto Ehtiyot AJ</t>
+          <t>Shodlik Mato MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>203652450</t>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000484256972001</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №128/26</t>
+          <t>Предоплата за товар по договору №131/26 от 13.07.2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1451,39 +1451,39 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>2042000</v>
+        <v>2026000</v>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>327320639</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000060946953001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ijtimoiy soliq</t>
+          <t>Оплата за упаковочные материалы, с/ф №9087</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1492,39 +1492,39 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>2042000</v>
+        <v>2269000</v>
       </c>
       <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ishonch Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>331078117</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000408581523001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>JShDS iyun oyi uchun</t>
+          <t>Предоплата за материалы по договору №203/26</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1532,40 +1532,40 @@
           <t>124</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n">
-        <v>1555000</v>
-      </c>
+      <c r="C34" s="2" t="n">
+        <v>3015000</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Omad Farm Savdo MChJ</t>
+          <t>Denov Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>268876078</t>
+          <t>368952869</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000357443680001</t>
+          <t>20208000595217441001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Shartnoma №133/26 bo'yicha oldindan to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №22/26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1573,40 +1573,40 @@
           <t>125</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>3207000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>2719000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>383089429</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000641564675001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №115/26</t>
+          <t>Shartnoma №263/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1616,38 +1616,38 @@
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
-        <v>4445000</v>
+        <v>1745000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Shodlik Mato MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №3072 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №153 15.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1655,40 +1655,40 @@
           <t>127</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n">
-        <v>1436000</v>
-      </c>
+      <c r="C37" s="2" t="n">
+        <v>2042000</v>
+      </c>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chust Qog'oz AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>259242091</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000318952522001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №257/26, QQS 12%</t>
+          <t>Ijtimoiy soliq iyun 2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1696,40 +1696,40 @@
           <t>128</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n">
-        <v>2046000</v>
-      </c>
+      <c r="C38" s="2" t="n">
+        <v>2042000</v>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №4107</t>
+          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1738,39 +1738,39 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>8113000</v>
+        <v>3490000</v>
       </c>
       <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sarbon Trans Servis XK</t>
+          <t>Ishonch Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>274109191</t>
+          <t>331078117</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000617602800001</t>
+          <t>20208000408581523001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7425</t>
+          <t>Оплата за товары согласно счет-фактуре №3288</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1780,38 +1780,38 @@
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>11227000</v>
+        <v>1699000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bunyodkor Plastik MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>306771966</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000169151588001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5706 20.07.2026, QQS bilan</t>
+          <t>Оплата за товар по с/ф №3107 от 16.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1821,38 +1821,38 @@
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>5333000</v>
+        <v>1406000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>247503341</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000631486661001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №7523 20.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по дог. №129/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1860,40 +1860,40 @@
           <t>132</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n">
-        <v>2961000</v>
-      </c>
+      <c r="C42" s="2" t="n">
+        <v>8655000</v>
+      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Omad Farm Savdo MChJ</t>
+          <t>Saodat Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>268876078</t>
+          <t>327320639</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000357443680001</t>
+          <t>20208000060946953001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2039 20.07.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №56/26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1903,21 +1903,21 @@
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>1941000</v>
+        <v>27786000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Omad Farm Savdo MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>268876078</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000357443680001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9619 20.07.2026, QQS bilan</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №54/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1944,21 +1944,21 @@
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>1348000</v>
+        <v>1070000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1968,14 +1968,14 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1162</t>
+          <t>Оплата за товар по с/ф №3439 от 20.07.2026, в т.ч. НС 12%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,40 +1983,40 @@
           <t>135</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>937000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>1833000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9496 20.07.2026, QQS bilan</t>
+          <t>QQS iyun 2026 uchun</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2024,40 +2024,40 @@
           <t>136</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>6707000</v>
-      </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n">
+        <v>9643000</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>383089429</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000641564675001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №130/26</t>
+          <t>Оплата по счет-фактуре №8075 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2065,23 +2065,23 @@
           <t>137</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>8852000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>1200000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Shodlik Mato MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>383089429</t>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000641564675001</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2091,14 +2091,14 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №9347</t>
+          <t>Предоплата за товар по договору №74/26 от 23.07.2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2108,38 +2108,38 @@
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>1025000</v>
+        <v>878000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bunyodkor Plastik MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>306771966</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000169151588001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №98/26, QQS 12%</t>
+          <t>Оплата по счет-фактур №3183 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2147,40 +2147,40 @@
           <t>139</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>23068000</v>
-      </c>
-      <c r="D49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n">
+        <v>11394000</v>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Oydin Avto Ehtiyot AJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>203652450</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000484256972001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №137/26</t>
+          <t>Оплата за продукцию по договору №285/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2190,21 +2190,21 @@
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>4801000</v>
+        <v>6377000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2214,14 +2214,14 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №346</t>
+          <t>Shartnoma №27/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2231,21 +2231,21 @@
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>1103000</v>
+        <v>3502000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Omad Farm Savdo MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>268876078</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000357443680001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №234 22.07.2026, QQS bilan</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №2125 ОТ 27.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2270,40 +2270,40 @@
           <t>142</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>1945000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>1282000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nihol Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>293888739</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000515912499001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июнь</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №5725 ОТ 27.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2313,21 +2313,21 @@
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>3440000</v>
+        <v>1253000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2337,14 +2337,14 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Shartnoma №58/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №78 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2354,38 +2354,38 @@
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>2057000</v>
+        <v>1248000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bahor Qurilish Materiallari MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>260098122</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000760955818001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6264 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №757 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2393,40 +2393,40 @@
           <t>145</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n">
-        <v>948000</v>
-      </c>
+      <c r="C55" s="2" t="n">
+        <v>716000</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Omad Farm Savdo MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>268876078</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000357443680001</t>
+          <t>20208000905830894001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №292/26, QQS 12%</t>
+          <t>Оплата за электроэнергию за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2436,21 +2436,21 @@
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>18357000</v>
+        <v>1144000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2460,14 +2460,14 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №218/26, QQS 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №44/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2475,40 +2475,40 @@
           <t>147</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>2632000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>1041000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sarbon Trans Servis XK</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>274109191</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000617602800001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №33/26</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №1771 28.07.2026, QQS BILAN</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2516,40 +2516,40 @@
           <t>148</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>2523000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>7362000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Omad Farm Savdo MChJ</t>
+          <t>Olmaliq Qurilish Materiallari XK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>268876078</t>
+          <t>327400977</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000357443680001</t>
+          <t>20208000272549219001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №275/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №7999</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2557,40 +2557,40 @@
           <t>149</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>716000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>1073000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Shodlik Mato MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000020184584001</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>Предоплата за товар по дог. №102/26 от 30.07.2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2598,40 +2598,40 @@
           <t>150</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>13905000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>1303000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sarbon Trans Servis XK</t>
+          <t>Shodlik Mato MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>274109191</t>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000617602800001</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №134/26</t>
+          <t>Предоплата за товар по договору №97/26 от 31.07.2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2639,40 +2639,35 @@
           <t>151</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>960000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>293754344</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №177/26, QQS 12%</t>
+          <t>ПЛАТА ЗА SMS-ИНФОРМИРОВАНИЕ</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2682,21 +2677,21 @@
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>8339000</v>
+        <v>3230000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2706,14 +2701,14 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №229/26, QQS 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №257/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2723,38 +2718,38 @@
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>5547000</v>
+        <v>1164000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Nihol Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>293888739</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000515912499001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №246/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №232/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2763,39 +2758,39 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>4573000</v>
+        <v>54414000</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oydin Avto Ehtiyot AJ</t>
+          <t>Ishonch Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>203652450</t>
+          <t>331078117</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000484256972001</t>
+          <t>20208000408581523001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №286/26</t>
+          <t>Оплата за транспортные услуги по договору №126/26</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2805,38 +2800,38 @@
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>3810000</v>
+        <v>4050000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Shodlik Mato MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>339786100</t>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000742103980001</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Оплата по /ф №6296 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №5088 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2844,40 +2839,40 @@
           <t>156</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n">
-        <v>1665000</v>
-      </c>
+      <c r="C66" s="2" t="n">
+        <v>3527000</v>
+      </c>
+      <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Ishonch Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>247503341</t>
+          <t>331078117</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000631486661001</t>
+          <t>20208000408581523001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2680 31.07.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №12/26</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2885,40 +2880,35 @@
           <t>157</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>1557000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>14516000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>293754344</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №107</t>
+          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2928,21 +2918,21 @@
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>1500000</v>
+        <v>2724000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sarbon Agro AJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>311906338</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000983322135001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2952,14 +2942,14 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №111 31.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №288/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2967,18 +2957,23 @@
           <t>159</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n">
+        <v>1379000</v>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Nihol Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>293888739</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000515912499001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2988,14 +2983,14 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Оплата за товар по счет-фактуре №7797 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3003,40 +2998,40 @@
           <t>160</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>2501000</v>
-      </c>
-      <c r="D70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n">
+        <v>1186000</v>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Oydin Avto Ehtiyot AJ</t>
+          <t>Barakali Non MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>203652450</t>
+          <t>350334106</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000484256972001</t>
+          <t>20208000148666189001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №226/26</t>
+          <t>Предоплата за товар по договору №132/26 от 10.08.2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3045,39 +3040,39 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>3586000</v>
+        <v>1111000</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>383089429</t>
+          <t>267719662</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000641564675001</t>
+          <t>20208000691515883001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №108/26</t>
+          <t>АРЕНДНАЯ ПЛАТА ЗА АВГУСТ 2026 Г. ПО ДОГ. №20/23</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3085,40 +3080,35 @@
           <t>162</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>2680000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Omad Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>268876078</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-5384)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000357443680001</t>
+          <t>16307000252614105417</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №172/26, QQS 12%</t>
+          <t>Kredit shartnomasi L-2024-5384 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3126,40 +3116,40 @@
           <t>163</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>2618000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>5525000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bunyodkor Plastik MChJ</t>
+          <t>Ishonch Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>306771966</t>
+          <t>331078117</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000169151588001</t>
+          <t>20208000408581523001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5301</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №7270</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3169,38 +3159,38 @@
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>2114000</v>
+        <v>7336000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Shodlik Mato MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2175</t>
+          <t>Оплата за продукцию по договору №108/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3209,22 +3199,22 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>1873000</v>
+        <v>3980000</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Ishonch Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>383089429</t>
+          <t>331078117</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000641564675001</t>
+          <t>20208000408581523001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3234,14 +3224,14 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №268/26</t>
+          <t>Оплта за упаковочные материалы, с/ф №9023</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3249,40 +3239,40 @@
           <t>166</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>2539000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>1045000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Barakali Non MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>383089429</t>
+          <t>350334106</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000641564675001</t>
+          <t>20208000148666189001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5126</t>
+          <t>Оплата за продукцию по договору №212/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3290,40 +3280,40 @@
           <t>167</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>3894000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>2788000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>383089429</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000641564675001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №249/26, QQS bilan</t>
+          <t>Предоплата за товар по дог. №31/26 от 17.08.2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3331,40 +3321,40 @@
           <t>168</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>14058000</v>
-      </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n">
+        <v>1082000</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sarbon Trans Servis XK</t>
+          <t>Barakali Non MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>274109191</t>
+          <t>350334106</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000617602800001</t>
+          <t>20208000148666189001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №123/26, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3734</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3372,40 +3362,40 @@
           <t>169</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>1208000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>1979000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2428 04.08.2026, QQS bilan</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3414,39 +3404,39 @@
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>5563000</v>
+        <v>1979000</v>
       </c>
       <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sarbon Trans Servis XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>274109191</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000617602800001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4033</t>
+          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3454,35 +3444,40 @@
           <t>171</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>14516000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>3308000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Saodat Metall Servis AJ</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №6020</t>
+          <t>Предоплата за товар по договору №255/26 от 18.08.2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3490,40 +3485,40 @@
           <t>172</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>1111000</v>
-      </c>
-      <c r="D82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n">
+        <v>14349000</v>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saodat Qurilish Materiallari XK</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>316213871</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000814220025001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov avgust</t>
+          <t>Оплата за товар по счет-фактуре №8169 от 19.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3533,38 +3528,38 @@
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>21098000</v>
+        <v>1158000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bunyodkor Plastik MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>306771966</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000169151588001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №178/26, QQS 12%</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №209/26 ОТ 19.08.2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3572,40 +3567,40 @@
           <t>174</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n">
-        <v>6139000</v>
-      </c>
+      <c r="C84" s="2" t="n">
+        <v>11868000</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Ishonch Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>247503341</t>
+          <t>331078117</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000631486661001</t>
+          <t>20208000408581523001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №121/26, QQS 12%</t>
+          <t>Оплата за сырье по договору №50/26 от 19.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3613,40 +3608,40 @@
           <t>175</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n">
-        <v>2467000</v>
-      </c>
+      <c r="C85" s="2" t="n">
+        <v>24684000</v>
+      </c>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Ishonch Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>331078117</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000408581523001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2139 10.08.2026, QQS bilan</t>
+          <t>Оплата за сырье по дог. №18/26 от 19.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3654,40 +3649,40 @@
           <t>176</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>1605000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>6497000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>383089429</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000641564675001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8474</t>
+          <t>ОПЛАТА ПО С/Ф №2706 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3696,39 +3691,39 @@
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>1927000</v>
+        <v>6259000</v>
       </c>
       <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sarbon Trans Servis XK</t>
+          <t>Ishonch Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>274109191</t>
+          <t>331078117</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000617602800001</t>
+          <t>20208000408581523001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №107/26</t>
+          <t>Предоплата за материалы по договору №55/26</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3736,35 +3731,40 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>5800000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>3235000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-5384)</t>
+          <t>Shodlik Mato MChJ</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>16307000252614105417</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-5384 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата по с/ф №1948 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3772,23 +3772,23 @@
           <t>179</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>6011000</v>
-      </c>
-      <c r="D89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n">
+        <v>2590000</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oydin Avto Ehtiyot AJ</t>
+          <t>Nihol Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>203652450</t>
+          <t>293888739</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000484256972001</t>
+          <t>20208000515912499001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3798,14 +3798,14 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1403</t>
+          <t>Shartnoma №70/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3815,38 +3815,38 @@
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>8161000</v>
+        <v>1127000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Angren Logistik MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>324209103</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000895252232001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6305</t>
+          <t>Shartnoma №235/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3856,21 +3856,21 @@
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>2972000</v>
+        <v>922000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3880,14 +3880,14 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №7270 11.08.2026, QQS BILAN</t>
+          <t>Оплата по счет-фактуре №4698 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3895,40 +3895,40 @@
           <t>182</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>856000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>694000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000905830894001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №4511</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3937,39 +3937,39 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>12620000</v>
+        <v>1816000</v>
       </c>
       <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>383089429</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000641564675001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2956</t>
+          <t>НДС за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3978,39 +3978,39 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>14143000</v>
+        <v>4994000</v>
       </c>
       <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oydin Avto Ehtiyot AJ</t>
+          <t>Ishonch Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>203652450</t>
+          <t>331078117</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000484256972001</t>
+          <t>20208000408581523001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №240/26, QQS bilan</t>
+          <t>Предоплата за материалы по договору №22/26</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4018,40 +4018,40 @@
           <t>185</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n">
-        <v>19961000</v>
-      </c>
+      <c r="C95" s="2" t="n">
+        <v>8179000</v>
+      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Saodat Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>327320639</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000060946953001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №8486 от 12.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за материалы по договору №297/26</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4061,21 +4061,21 @@
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>1851000</v>
+        <v>5002000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4085,14 +4085,14 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Shatnoma №144/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №127/26 от 25.08.2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4100,40 +4100,40 @@
           <t>187</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>11133000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>1675000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>383089429</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000641564675001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1531</t>
+          <t>Mahsulot uchun to'lov, shartnoma №190/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4141,40 +4141,40 @@
           <t>188</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>1979000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>1389000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shodlik Mato MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>Предоплата за товар по договору №70/26 от 26.08.2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4182,40 +4182,40 @@
           <t>189</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>1979000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>7457000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>JShDS iyul oyi uchun</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6610</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4225,38 +4225,38 @@
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>1372000</v>
+        <v>3547000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Nihol Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>293888739</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000515912499001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №268/26, QQS 12%</t>
+          <t>Оплата за продукцию по дог. №8/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4264,40 +4264,40 @@
           <t>191</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n">
-        <v>1505000</v>
-      </c>
-      <c r="D101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n">
+        <v>1225000</v>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oydin Avto Ehtiyot AJ</t>
+          <t>Shodlik Mato MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>203652450</t>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000484256972001</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №61/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4956</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4305,40 +4305,40 @@
           <t>192</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>10442000</v>
-      </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n">
+        <v>21589000</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sarbon Trans Servis XK</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>274109191</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000617602800001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №277/26</t>
+          <t>Оплата за продукцию по договору №98/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4348,38 +4348,38 @@
       </c>
       <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="n">
-        <v>1110000</v>
+        <v>7400000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Shodlik Mato MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1737 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №129/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4389,38 +4389,38 @@
       </c>
       <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="n">
-        <v>2191000</v>
+        <v>3068000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Shodlik Mato MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9398 19.08.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №2108 от 28.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4430,38 +4430,38 @@
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>2061000</v>
+        <v>18168000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Shodlik Mato MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №7025 19.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по дог. №261/26 от 31.08.2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4471,38 +4471,38 @@
       </c>
       <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="n">
-        <v>1869000</v>
+        <v>9894000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Shodlik Mato MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Shartnoma №174/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartn. №64/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4512,21 +4512,21 @@
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>872000</v>
+        <v>4769000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4536,14 +4536,14 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3859 19.08.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5065 31.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4551,40 +4551,40 @@
           <t>198</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>2786000</v>
-      </c>
-      <c r="D108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n">
+        <v>4760000</v>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Jizzax Oziq-ovqat Savdo XK</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>299363596</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000878917545001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Предоплата за материалыпо договору №40/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №190/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4594,38 +4594,38 @@
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>7592000</v>
+        <v>2248000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Shodlik Mato MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №55/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №5900 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4634,39 +4634,34 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>1859000</v>
+        <v>300000</v>
       </c>
       <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>НДС за июль 2026 г.</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4674,40 +4669,40 @@
           <t>201</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>14677000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>5974000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>383089429</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000641564675001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1516</t>
+          <t>Оплата за товар по счет-фактуре №3427 от 01.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4717,38 +4712,38 @@
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>7494000</v>
+        <v>1896000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Barakali Non MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>350334106</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000148666189001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9074</t>
+          <t>Оплата за продукцию по договору №273/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4756,40 +4751,40 @@
           <t>203</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n">
-        <v>3015000</v>
-      </c>
+      <c r="C113" s="2" t="n">
+        <v>2840000</v>
+      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Chust Poligraf MChJ</t>
+          <t>Ishonch Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>396310781</t>
+          <t>331078117</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000764085815001</t>
+          <t>20208000408581523001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8313</t>
+          <t>Оплата за транспортные услуги по договору №62/26</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4799,21 +4794,21 @@
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>1957000</v>
+        <v>6354000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Omad Farm Savdo MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>268876078</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000357443680001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4823,14 +4818,14 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1985</t>
+          <t>Оплата по с/ф №4263 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4838,40 +4833,40 @@
           <t>205</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>797000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>3521000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Omad Farm Savdo MChJ</t>
+          <t>Xiva Agro MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>268876078</t>
+          <t>290633879</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000357443680001</t>
+          <t>20208000332213541001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9460 24.08.2026, QQS bilan</t>
+          <t>Tovarlar uchun to'lov h/f №7676</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4880,39 +4875,39 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>694000</v>
+        <v>5752000</v>
       </c>
       <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Ishonch Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>331078117</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000020184584001</t>
+          <t>20208000408581523001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov avgust</t>
+          <t>Предоплата за материалы по договору №2/26</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4920,40 +4915,40 @@
           <t>207</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
-        <v>12573000</v>
-      </c>
-      <c r="D117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n">
+        <v>3683000</v>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Oydin Avto Ehtiyot AJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>203652450</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000484256972001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №115/26 от 24.08.2026, НДС 12%</t>
+          <t>Shartnoma №206/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4961,40 +4956,40 @@
           <t>208</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n">
-        <v>3955000</v>
-      </c>
+      <c r="C118" s="2" t="n">
+        <v>5153000</v>
+      </c>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Saodat Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>327320639</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000060946953001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8623</t>
+          <t>Предоплата за материалы по договору №269/26</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5002,40 +4997,35 @@
           <t>209</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n">
-        <v>3543000</v>
-      </c>
+      <c r="C119" s="2" t="n">
+        <v>16160000</v>
+      </c>
+      <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>293754344</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3218</t>
+          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5043,40 +5033,40 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n">
-        <v>1435000</v>
-      </c>
+      <c r="C120" s="2" t="n">
+        <v>46031000</v>
+      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Ishonch Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>331078117</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000408581523001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №98/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №4936</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5084,40 +5074,40 @@
           <t>211</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>2080000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>1237000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bahor Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>260098122</t>
+          <t>267719662</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000760955818001</t>
+          <t>20208000691515883001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Shartnoma №44/26 bo'yicha oldindan to'lov</t>
+          <t>Аренда помещения за сентябрь, дог. №20/23</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5125,40 +5115,40 @@
           <t>212</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>4805000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>2647000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Jizzax Oziq-ovqat Savdo XK</t>
+          <t>Nihol Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>299363596</t>
+          <t>293888739</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000878917545001</t>
+          <t>20208000515912499001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №114/26</t>
+          <t>Оплата по счет-фактуре №7263 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5166,40 +5156,35 @@
           <t>213</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>21391000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>293754344</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-5384)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>16307000252614105417</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov,shartnoma №136/26, QQS 12%</t>
+          <t>Kredit shartnomasi L-2024-5384 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5209,21 +5194,21 @@
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>13431000</v>
+        <v>48880000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5233,14 +5218,14 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6296</t>
+          <t>Предоплата за товар по договору №67/26 от 11.09.2026</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5250,38 +5235,38 @@
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>2777000</v>
+        <v>44900000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Barakali Non MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>350334106</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000148666189001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Shartnoma №249/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №9856 от 11.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5289,40 +5274,40 @@
           <t>216</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>2537000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>40901000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Ishonch Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>331078117</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000408581523001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4898 31.08.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по дог. №174/26</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5332,38 +5317,38 @@
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>1329000</v>
+        <v>3233000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Nihol Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>293888739</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000515912499001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Shartnoma №55/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №6531 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5371,35 +5356,40 @@
           <t>218</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n">
+        <v>1904000</v>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Saodat Metall Servis AJ</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Предоплата за товар по договору №289/26 от 14.09.2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5407,40 +5397,40 @@
           <t>219</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>1530000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>1451000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>383089429</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000641564675001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №89/26</t>
+          <t>Предоплата за товар по договору №239/26 от 14.09.2026</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5449,39 +5439,39 @@
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>4939000</v>
+        <v>5730000</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
+          <t>Saodat Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>383089429</t>
+          <t>327320639</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000641564675001</t>
+          <t>20208000060946953001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3795</t>
+          <t>Оплата за товары согласно счет-фактуре №9948</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5489,40 +5479,40 @@
           <t>221</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n">
-        <v>3920000</v>
-      </c>
+      <c r="C131" s="2" t="n">
+        <v>12022000</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Denov Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>368952869</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000595217441001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9945 01.09.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по дог. №248/26</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5530,40 +5520,40 @@
           <t>222</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>2231000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>2204000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>247503341</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000631486661001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №228/26, QQS 12%</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5572,39 +5562,39 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>2093000</v>
+        <v>2204000</v>
       </c>
       <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Oydin Avto Ehtiyot AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>203652450</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000484256972001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №135/26</t>
+          <t>НДФЛ за август 2026</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5613,39 +5603,39 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>4796000</v>
+        <v>6971000</v>
       </c>
       <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Jizzax Oziq-ovqat Savdo XK</t>
+          <t>Ishonch Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>299363596</t>
+          <t>331078117</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000878917545001</t>
+          <t>20208000408581523001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №9/26 от 02.09.2026, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №7183</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5655,21 +5645,21 @@
       </c>
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="n">
-        <v>4010000</v>
+        <v>2240000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5679,14 +5669,14 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №227/26 от 03.09.2026</t>
+          <t>Предоплата за товар по договору №244/26 от 17.09.2026</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5696,38 +5686,38 @@
       </c>
       <c r="C136" s="2" t="n"/>
       <c r="D136" s="2" t="n">
-        <v>1768000</v>
+        <v>4715000</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Omad Farm Savdo MChJ</t>
+          <t>Shodlik Mato MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>268876078</t>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000357443680001</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №42/26, QQS 12%</t>
+          <t>Оплата за товар по с/ф №3833 от 18.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5737,21 +5727,21 @@
       </c>
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="n">
-        <v>1375000</v>
+        <v>2707000</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5761,14 +5751,14 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Shartnoma №222/26 b'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №77/26 от 21.09.2026</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5777,39 +5767,39 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>3896000</v>
+        <v>5532000</v>
       </c>
       <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Jizzax Oziq-ovqat Savdo XK</t>
+          <t>Ishonch Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>299363596</t>
+          <t>331078117</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000878917545001</t>
+          <t>20208000408581523001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №87/26, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №214/26</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5818,39 +5808,39 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>8511000</v>
+        <v>1980000</v>
       </c>
       <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sarbon Trans Servis XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>274109191</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000617602800001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №103/26</t>
+          <t>Уплата налога на добавленную тоимость за август</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5858,35 +5848,40 @@
           <t>230</t>
         </is>
       </c>
-      <c r="C140" s="2" t="n">
-        <v>16160000</v>
-      </c>
-      <c r="D140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n">
+        <v>2630000</v>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Saodat Metall Servis AJ</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Предоплата за товар по договору №182/26 от 23.09.2026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5896,38 +5891,38 @@
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>7110000</v>
+        <v>7216000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Farovon Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>209812257</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000095581892001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6165 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по дог. №143/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5935,40 +5930,40 @@
           <t>232</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n">
-        <v>4919000</v>
-      </c>
+      <c r="C142" s="2" t="n">
+        <v>773000</v>
+      </c>
+      <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000905830894001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2060 07.09.2026, QQS bilan</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5978,38 +5973,38 @@
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>3771000</v>
+        <v>8959000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Shodlik Mato MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>387607863</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000744368086001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №208/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №5515 от 25.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6019,21 +6014,21 @@
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>3765000</v>
+        <v>7266000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Ziyo Metall Servis XK</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>375274009</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000792725492001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6043,14 +6038,14 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Shartnoma №270/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №2934 от 28.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6060,21 +6055,21 @@
       </c>
       <c r="C145" s="2" t="n"/>
       <c r="D145" s="2" t="n">
-        <v>1750000</v>
+        <v>3434000</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Saodat Metall Servis AJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>275434470</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000083224472001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6084,14 +6079,14 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №3599 07.09.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №8566 за поставенный товар</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6101,38 +6096,38 @@
       </c>
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="n">
-        <v>1104000</v>
+        <v>4870000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
+          <t>Nihol Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>293754344</t>
+          <t>293888739</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>20208000515912499001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №122/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №3256 от 29.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6140,1935 +6135,54 @@
           <t>237</t>
         </is>
       </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>2459000</v>
-      </c>
+      <c r="C147" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>293754344</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000070832244001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>SHARTNOMA №213/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="n">
-        <v>9270000</v>
-      </c>
-      <c r="D148" s="2" t="n"/>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>383089429</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>20208000641564675001</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №214/26</t>
-        </is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="n">
+        <v>470689000</v>
+      </c>
+      <c r="D148" s="4" t="n">
+        <v>469089000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="n">
-        <v>1237000</v>
-      </c>
-      <c r="D149" s="2" t="n"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Saodat Qurilish Materiallari XK</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>316213871</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>20208000814220025001</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartnoma №13/23</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>09.09.2026</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="n">
-        <v>1939000</v>
-      </c>
-      <c r="D150" s="2" t="n"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Oydin Avto Ehtiyot AJ</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>203652450</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>20208000484256972001</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Предоплата за матриалы по договору №199/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>10.09.2026</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="n"/>
-      <c r="D151" s="2" t="n">
-        <v>1791000</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Bunyodkor Polimer MChJ</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>339786100</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>20208000742103980001</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №118/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>10.09.2026</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="n"/>
-      <c r="D152" s="2" t="n">
-        <v>1643000</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>293754344</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>20208000070832244001</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1879 10.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>10.09.2026</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n">
-        <v>1632000</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Omad Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>268876078</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>20208000357443680001</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1726</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>10.09.2026</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="n">
-        <v>1977000</v>
-      </c>
-      <c r="D154" s="2" t="n"/>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Sarbon Trans Servis XK</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>274109191</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>20208000617602800001</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Tovarlar uchun to'lov h/f №6305</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>10.09.2026</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="n">
-        <v>5800000</v>
-      </c>
-      <c r="D155" s="2" t="n"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-5384)</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>16307000252614105417</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Kredit shartnomasi L-2024-5384 bo'yicha navbatdagi to'lov (09.2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>11.09.2026</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n">
-        <v>1685000</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Bunyodkor Plastik MChJ</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>306771966</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>20208000169151588001</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, h/f №3964 11.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>48262000</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>293754344</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>20208000070832244001</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №298/26, QS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n">
-        <v>3116000</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>247503341</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>20208000631486661001</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №5018 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="n"/>
-      <c r="D159" s="2" t="n">
-        <v>2541000</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>293754344</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>20208000070832244001</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9038 14.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="n"/>
-      <c r="D160" s="2" t="n">
-        <v>1202000</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Yulduz Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>228273206</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>20208000930609469001</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Shartnoma №232/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="n">
-        <v>2204000</v>
-      </c>
-      <c r="D161" s="2" t="n"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Ijtimoiy soliq avgust 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n">
-        <v>2204000</v>
-      </c>
-      <c r="D162" s="2" t="n"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>JISMONIY SHAXSLAR DAROMAD SOLIG'I AVGUST 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n">
-        <v>2576000</v>
-      </c>
-      <c r="D163" s="2" t="n"/>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>383089429</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>20208000641564675001</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №287/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v>4488000</v>
-      </c>
-      <c r="D164" s="2" t="n"/>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>383089429</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>20208000641564675001</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №31/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v>23547000</v>
-      </c>
-      <c r="D165" s="2" t="n"/>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Oydin Avto Ehtiyot AJ</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>203652450</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>20208000484256972001</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №91/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>15.09.2026</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="n"/>
-      <c r="D166" s="2" t="n">
-        <v>4353000</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>293754344</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>20208000070832244001</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №225/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="n">
-        <v>1532000</v>
-      </c>
-      <c r="D167" s="2" t="n"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Sarbon Trans Servis XK</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>274109191</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>20208000617602800001</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartn. №120/26, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="n">
-        <v>1607000</v>
-      </c>
-      <c r="D168" s="2" t="n"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>383089429</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>20208000641564675001</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №297/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>17.09.2026</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="n"/>
-      <c r="D169" s="2" t="n">
-        <v>1483000</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Omad Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>268876078</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>20208000357443680001</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №41/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>17.09.2026</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="n">
-        <v>1457000</v>
-      </c>
-      <c r="D170" s="2" t="n"/>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>383089429</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>20208000641564675001</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №74/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>18.09.2026</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="n"/>
-      <c r="D171" s="2" t="n">
-        <v>2831000</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Andijon Avto Savdo XK</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>205855442</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>20208000823607028001</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №58/26 от 18.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>18.09.2026</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="n"/>
-      <c r="D172" s="2" t="n">
-        <v>2442000</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>293754344</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>20208000070832244001</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3385</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>18.09.2026</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="n">
-        <v>3196000</v>
-      </c>
-      <c r="D173" s="2" t="n"/>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Jizzax Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>299363596</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>20208000878917545001</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №6650</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="n"/>
-      <c r="D174" s="2" t="n">
-        <v>4064000</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>293754344</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>20208000070832244001</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №179/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="n">
-        <v>2336000</v>
-      </c>
-      <c r="D175" s="2" t="n"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>383089429</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>20208000641564675001</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №157/26, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="n">
-        <v>2573000</v>
-      </c>
-      <c r="D176" s="2" t="n"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>383089429</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>20208000641564675001</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №19/26, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="n"/>
-      <c r="D177" s="2" t="n">
-        <v>2746000</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>293754344</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>20208000070832244001</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №88/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="n">
-        <v>55915000</v>
-      </c>
-      <c r="D178" s="2" t="n"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>383089429</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>20208000641564675001</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по дог. №217/26 от 22.09.2026, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="n"/>
-      <c r="D179" s="2" t="n">
-        <v>3867000</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>293754344</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>20208000070832244001</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1243</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="n">
-        <v>2021000</v>
-      </c>
-      <c r="D180" s="2" t="n"/>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Уплата налога на добавленную стоимость за август</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="n">
-        <v>2501000</v>
-      </c>
-      <c r="D181" s="2" t="n"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>383089429</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>20208000641564675001</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №20/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>24.09.2026</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="n"/>
-      <c r="D182" s="2" t="n">
-        <v>2271000</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>293754344</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>20208000070832244001</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>Оплата за товар по с/ф №987 от 24.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>25.09.2026</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="n">
-        <v>773000</v>
-      </c>
-      <c r="D183" s="2" t="n"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>20208000020184584001</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>Elektr energiyasi uchun to'lov sentyabr</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>25.09.2026</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="n">
-        <v>3616000</v>
-      </c>
-      <c r="D184" s="2" t="n"/>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>383089429</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>20208000641564675001</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №150/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="n"/>
-      <c r="D185" s="2" t="n">
-        <v>8635000</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Omad Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>268876078</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>20208000357443680001</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Shartnoma №45/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="n"/>
-      <c r="D186" s="2" t="n">
-        <v>6474000</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>247503341</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>20208000631486661001</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №67/26 от 28.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="n"/>
-      <c r="D187" s="2" t="n">
-        <v>2132000</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>293754344</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>20208000070832244001</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>Shartnoma №51/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="n"/>
-      <c r="D188" s="2" t="n">
-        <v>3467000</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>293754344</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>20208000070832244001</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>Shartnoma №47/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="n"/>
-      <c r="D189" s="2" t="n">
-        <v>1917000</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>293754344</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>20208000070832244001</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №257/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="n">
-        <v>2285000</v>
-      </c>
-      <c r="D190" s="2" t="n"/>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Qo'qon Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>383089429</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>20208000641564675001</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №65/26, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="n"/>
-      <c r="D191" s="2" t="n">
-        <v>18753000</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Chust Qog'oz AJ</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>259242091</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>20208000318952522001</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №287/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="n"/>
-      <c r="D192" s="2" t="n">
-        <v>2904000</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Farg'ona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>293754344</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>20208000070832244001</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7509</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D193" s="2" t="n"/>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Oqsaroy Bank ATB</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="n">
-        <v>486995000</v>
-      </c>
-      <c r="D194" s="4" t="n">
-        <v>485395000</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C195" s="4" t="n">
+      <c r="C149" s="4" t="n">
         <v>14000000</v>
       </c>
-      <c r="D195" s="4" t="n"/>
+      <c r="D149" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
